--- a/output/pdf_financials_xlsx/BAMI.xlsx
+++ b/output/pdf_financials_xlsx/BAMI.xlsx
@@ -1498,19 +1498,19 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>96.95</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>85.794</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>72.541</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>12.02</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>54.477</v>
       </c>
     </row>
     <row r="35">
@@ -1554,19 +1554,19 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>96.95</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>85.794</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>72.541</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>12.02</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>54.477</v>
       </c>
     </row>
     <row r="37">
@@ -1890,19 +1890,19 @@
         <v>113.865</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>161.596</v>
+        <v>64.646</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>163.308</v>
+        <v>77.514</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>214.147</v>
+        <v>141.606</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>22.568</v>
+        <v>10.548</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>62.242</v>
+        <v>7.765</v>
       </c>
     </row>
     <row r="49">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/BAMI.xlsx
+++ b/output/pdf_financials_xlsx/BAMI.xlsx
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>8.273</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>10.699</v>
@@ -1336,10 +1336,10 @@
         <v>5.957</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2.508</v>
+        <v>5.097</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>3.228</v>
+        <v>6.266</v>
       </c>
     </row>
     <row r="29">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.345</v>
+        <v>-5.928</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>17.951</v>
@@ -1368,10 +1368,10 @@
         <v>-13.848</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>14.919</v>
+        <v>17.508</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>17.509</v>
+        <v>20.547</v>
       </c>
     </row>
     <row r="30">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.4040532833421495</v>
+        <v>-1.021419131621434</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>5.899481071772474</v>
@@ -3355,25 +3355,25 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>8.18</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>8.641999999999999</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>10.699</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>5.957</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>5.097</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>6.266</v>
       </c>
     </row>
     <row r="101">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>14.99</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.475</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -9466,7 +9466,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -9515,7 +9519,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -9615,7 +9623,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -11123,7 +11131,11 @@
           <t>Additions to intangible assets (Note 8)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -11935,7 +11947,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13521,11 +13533,7 @@
           <t>Amortization of other intangible assets (note 8)</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>AmortizationOfIntangibles</t>
-        </is>
-      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -14754,7 +14762,11 @@
           <t>Cumulative translation adjustments on foreign operations (790) 2,172 Amortization of intangible assets (note 9)</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E207" s="5" t="n">
         <v>8.18</v>
       </c>
@@ -16301,7 +16313,11 @@
           <t>Proceeds from disposal of property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E238" s="5" t="n">
         <v>14.99</v>
       </c>

--- a/output/pdf_financials_xlsx/BAMI.xlsx
+++ b/output/pdf_financials_xlsx/BAMI.xlsx
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>6.051</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
@@ -2137,10 +2137,10 @@
         <v>0</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>7.893</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>10.977</v>
       </c>
     </row>
     <row r="57">
@@ -2165,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>4.661</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>5.859</v>
       </c>
     </row>
     <row r="58">
@@ -2361,10 +2361,10 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>10.144</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>20.799</v>
       </c>
     </row>
     <row r="65">
@@ -2445,10 +2445,10 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>17.535</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>33.518</v>
       </c>
     </row>
     <row r="68">
@@ -3523,19 +3523,19 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-13.205</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>96.179</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-188.759</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>48.077</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-61.668</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>0</v>
@@ -3551,19 +3551,19 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.721</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>5.449</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>4.594</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>1.089</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>3.437</v>
       </c>
       <c r="G107" s="3" t="n">
         <v>3.419</v>
@@ -3952,13 +3952,13 @@
         <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-0.035</v>
       </c>
       <c r="F121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
@@ -9927,7 +9927,11 @@
           <t>Deferred tax expense (Note 22)</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -10429,7 +10433,11 @@
           <t>Share repurchases</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -11751,7 +11759,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -12100,7 +12112,11 @@
           <t>Share-based compensation expense (note 12)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -12541,7 +12557,11 @@
           <t>Change in non-cash balances related to operations (note 27)</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -12888,7 +12908,11 @@
           <t>Repurchase of common shares (note 11)</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -13778,7 +13802,11 @@
           <t>Deferred income tax expense (note 28)</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -13827,7 +13855,11 @@
           <t>Change in non-cash balances related to operations (note 30)</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -14270,7 +14302,11 @@
           <t>Proceeds from share issuance, net (note 11)</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -14866,7 +14902,11 @@
           <t>Share-based compensation expense (note 13)</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E209" s="5" t="n">
         <v>0.721</v>
       </c>
@@ -15209,7 +15249,11 @@
           <t>Deferred income tax expense (note 28)</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E216" s="5" t="n">
         <v>-7.917</v>
       </c>
@@ -15609,7 +15653,11 @@
           <t>Change in non-cash balances related to operations (note 30)</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E224" s="5" t="n">
         <v>-13.205</v>
       </c>
@@ -16668,7 +16716,11 @@
           <t>Net income from discontinued operations</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -17672,7 +17724,11 @@
           <t>Deferred income tax recovery (note 25)</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
